--- a/NU-AURA_QA_Validation_Report.xlsx
+++ b/NU-AURA_QA_Validation_Report.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend UI-UX Validation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend API Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E2E Test Scenarios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Schema Coverage" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defects &amp; Recommendations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Validation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live UI Test Results" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixes Applied" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Role-Based Testing" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form Validation Testing" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Re-Audit Mar 19" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Before vs After Comparison" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Code Review Audit" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deployment Readiness" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Frontend UI-UX Validation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Backend API Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="E2E Test Scenarios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Validation Schema Coverage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Defects &amp; Recommendations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Security Validation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Live UI Test Results" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Fixes Applied" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Role-Based Testing" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Form Validation Testing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="QA Re-Audit Mar 19" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Before vs After Comparison" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Final Code Review Audit" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Deployment Readiness" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frontend UI-UX Validation'!$A$3:$L$133</definedName>
@@ -41,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,8 +122,11 @@
       <color rgb="001B5E20"/>
       <sz val="12"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -173,6 +176,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001B5E20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -304,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -380,6 +389,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7525,6 +7537,12 @@
 • Design system fully compliant</t>
         </is>
       </c>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -23540,7 +23558,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>BACKLOG</t>
         </is>
       </c>
     </row>
@@ -23575,9 +23593,9 @@
           <t>Fix CSS variable class syntax — remove trailing numeric suffix</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>FIXED — Removed trailing 50 from CSS variable class syntax</t>
         </is>
       </c>
     </row>
@@ -23612,9 +23630,9 @@
           <t>Add focus trap (react-focus-lock) and aria attributes to Modal component</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>FIXED — Added focus trap, keyboard nav, auto-focus, and focus restoration to Modal component</t>
         </is>
       </c>
     </row>
@@ -23649,9 +23667,9 @@
           <t>Wrap tables in ResponsiveTable/horizontal scroll container</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>FIXED — Changed overflow-hidden to overflow-x-auto for table container</t>
         </is>
       </c>
     </row>
@@ -23686,9 +23704,9 @@
           <t>Add PermissionGate wrapper to each module card</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>FIXED — Added PermissionGate wrapper on module cards</t>
         </is>
       </c>
     </row>
@@ -23723,9 +23741,9 @@
           <t>Replace bg-purple-100, text-purple-800 etc. with CSS variable equivalents</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>FIXED — Replaced hardcoded purple/green colors with CSS variables</t>
         </is>
       </c>
     </row>
@@ -23760,9 +23778,9 @@
           <t>Add EmptyState component with "Create your first role" CTA</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>FIXED — Added empty state with message when no roles found</t>
         </is>
       </c>
     </row>
@@ -23797,9 +23815,9 @@
           <t>Change POST endpoints to return HttpStatus.CREATED</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>FIXED — POST endpoints now return HttpStatus.CREATED</t>
         </is>
       </c>
     </row>
@@ -24167,7 +24185,7 @@
           <t>Fixed: Error check now takes priority over loading state; replaced Loader2 with NuAuraLoader</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="31" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
@@ -24204,7 +24222,7 @@
           <t>Fixed: Added "Try again" button below error message</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="31" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
@@ -24241,9 +24259,9 @@
           <t>Map common HTTP status codes to user-friendly messages in error handler</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -24278,9 +24296,9 @@
           <t>Create shared ErrorBoundary component with consistent retry/refresh buttons</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -24315,9 +24333,9 @@
           <t>Fix feature-flag.service.ts import + add proper types to useFeatureFlags hooks</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>VERIFIED CLEAN — No TS errors found in feature-flag module</t>
         </is>
       </c>
     </row>
@@ -24352,7 +24370,7 @@
           <t>FIXED: Added inline error display inside password card. Also recommend migrating to RHF+Zod.</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="31" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
@@ -24389,9 +24407,9 @@
           <t>Add toast notification (react-hot-toast or similar) for API success/failure in employee create mutation</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G27" s="31" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -24428,7 +24446,7 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FALSE POSITIVE</t>
         </is>
       </c>
     </row>
@@ -24465,7 +24483,7 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>RESOLVED — SSO only</t>
         </is>
       </c>
     </row>
@@ -24500,7 +24518,7 @@
           <t>Removed Level column (redundant), kept Actions as last visible column. 7 columns now fit viewport.</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="31" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
@@ -24537,7 +24555,7 @@
           <t>Added InlineRoleEditor with pencil icon in Actions column. Opens modal with multi-select role grid + permission preview.</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="31" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
